--- a/MASTER_DOWNTIME_PABRIK.xlsx
+++ b/MASTER_DOWNTIME_PABRIK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>No</t>
   </si>
@@ -65,6 +65,48 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>Takurobo</t>
+  </si>
+  <si>
+    <t>P63</t>
+  </si>
+  <si>
+    <t>04/Jun/26 08:43:16</t>
+  </si>
+  <si>
+    <t>00:00:05</t>
+  </si>
+  <si>
+    <t>TAKUROBO</t>
+  </si>
+  <si>
+    <t>P59</t>
+  </si>
+  <si>
+    <t>04/Jun/26 08:59:26</t>
+  </si>
+  <si>
+    <t>00:03:29</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>p59</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>Not Filled In Yet</t>
+  </si>
+  <si>
+    <t>09.53</t>
+  </si>
+  <si>
+    <t>04:09:30</t>
   </si>
 </sst>
 </file>
@@ -90,7 +132,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -105,6 +147,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -127,12 +174,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -474,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -556,8 +606,113 @@
         <v>17</v>
       </c>
     </row>
+    <row r="3" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/MASTER_DOWNTIME_PABRIK.xlsx
+++ b/MASTER_DOWNTIME_PABRIK.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="34">
   <si>
     <t>No</t>
   </si>
@@ -107,6 +107,12 @@
   </si>
   <si>
     <t>04:09:30</t>
+  </si>
+  <si>
+    <t>04/Jun/26 14:16:41</t>
+  </si>
+  <si>
+    <t>00:07:04</t>
   </si>
 </sst>
 </file>
@@ -524,7 +530,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -711,6 +717,41 @@
         <v>17</v>
       </c>
     </row>
+    <row r="6" ht="20" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
